--- a/TestData/LV_TMTT0011418_VerifyTASSupervisorCanMoreThan24hoursForOneDayForAssociatesWithTitleTAGOutsourcedContractor.xlsx
+++ b/TestData/LV_TMTT0011418_VerifyTASSupervisorCanMoreThan24hoursForOneDayForAssociatesWithTitleTAGOutsourcedContractor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMittal0207\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6476351B-6BCB-4E87-9436-5D9F2ADD53A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269075B0-CDBB-4EBD-A6E4-930D6629CBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -83,6 +83,9 @@
     <t>Project Bend-Bernhard Capital Partners Management-FVA-109081</t>
   </si>
   <si>
+    <t>Project Clear-LucidHealth-FVA-105379</t>
+  </si>
+  <si>
     <t>Christy Skaar</t>
   </si>
   <si>
@@ -96,9 +99,6 @@
   </si>
   <si>
     <t>Time Record Manager</t>
-  </si>
-  <si>
-    <t>Bartush-Cotton Creek Capital Management LLC-FVA-110095</t>
   </si>
 </sst>
 </file>
@@ -808,19 +808,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -832,19 +832,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80D8A544-D0E8-40E8-BC38-28214023EEFB}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -855,19 +855,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F27E0078-49F4-4994-AA79-1F94FF26470C}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -878,14 +878,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -893,9 +893,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -913,17 +913,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -936,14 +936,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -956,9 +956,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -966,7 +966,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -982,13 +982,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -996,9 +996,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -1012,12 +1012,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1025,9 +1025,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
